--- a/education_forms/027_preschool_director_evaluation_form--education_forms.xlsx
+++ b/education_forms/027_preschool_director_evaluation_form--education_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,15 +510,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>preschool_director_rating</t>
+          <t>overall_rating</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>overall_rating</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Overall Rating</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rate the director's overall performance</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -533,15 +537,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>preschool_director_rating</t>
+          <t>director_communication</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>overall_rating</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Director's Communication</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How well does the director communicate with students and parents?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -556,15 +564,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>director_communication</t>
+          <t>director_friendliness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>director_communication</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Director's Friendliness</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>How approachable and friendly is the director?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -579,15 +591,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>director_friendliness</t>
+          <t>teacher_support</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>director_friendliness</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Teacher Support</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>How well do teachers support each other and the director?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -602,15 +618,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>teacher_support</t>
+          <t>teacher_expertise</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>teacher_support</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Teacher Expertise</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>How much expertise do the teachers have?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -625,15 +645,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>teacher_expertise</t>
+          <t>facilities_availability</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>teacher_expertise</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Facilities Availability</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How well are the facilities maintained and available for use?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -648,15 +672,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>director_conflict_resilience</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Director's Conflict Handling</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>How well does the director handle conflicts?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -671,15 +699,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>director_availability</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Director's Availability</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>How available is the director to answer questions?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -694,15 +726,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>director_patience</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Director's Patience</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>How patient is the director with the students?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -717,15 +753,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>director_time_management</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Director's Time Management</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>How effectively does the director manage time?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -740,15 +780,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>director_leadership</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Director's Leadership</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>How well does the director lead the school?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -763,15 +807,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>director_attitude</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Director's Attitude</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>What is the director's overall attitude towards the school?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -786,15 +834,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>emergency_situations</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Director's Emergency Handling</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>How well does the director handle emergency situations?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -809,15 +861,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>diversity_inclusion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Director's Commitment to Diversity and Inclusion</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>How well does the director promote diversity and inclusion?</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -832,15 +888,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>classroom_environment</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Director's Classroom Environment</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>How safe and engaging is the classroom environment?</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -855,15 +915,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>student_engagement</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Director's Student Engagement</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>How well does the director engage the students in activities?</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -878,15 +942,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>behavior_management</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Director's Behavior Management</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>How well does the director manage classroom behavior?</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -901,177 +969,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>overall_effectiveness</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Director's Overall Effectiveness</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>What is the director's overall effectiveness?</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
